--- a/public/plantilla-cal-proveedores.xlsx
+++ b/public/plantilla-cal-proveedores.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evaluación Proveedores" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,10 +16,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="165" formatCode="#,##0.##"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
-    <numFmt numFmtId="168" formatCode="hh:mm"/>
+    <numFmt numFmtId="164" formatCode="#,##0.##"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="hh:mm"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -600,7 +600,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="187">
+  <cellXfs count="189">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
@@ -637,7 +637,7 @@
     <xf numFmtId="14" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -725,34 +725,34 @@
     <xf numFmtId="14" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="167" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -926,70 +926,70 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="20" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="21" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="19" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="21" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="20" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="20" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="21" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="20" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="165" fontId="20" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -1063,55 +1063,61 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="21" fillId="0" borderId="19" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="165" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="21" fillId="0" borderId="19" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="168" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1122,7 +1128,7 @@
     <cellStyle name="Normal 4" xfId="4"/>
     <cellStyle name="Normal 6 2" xfId="5"/>
   </cellStyles>
-  <dxfs count="856">
+  <dxfs count="859">
     <dxf>
       <font>
         <b val="1"/>
@@ -11392,6 +11398,42 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFF8CBAD"/>
           <bgColor rgb="FFF8CBAD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="007A4F00"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFEB9C"/>
+          <bgColor rgb="00FFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -11402,32 +11444,32 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>862393</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>131445</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Image 1" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>2</col>
+      <colOff>862393</colOff>
+      <row>5</row>
+      <rowOff>131445</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="0"/>
           <a:ext cx="2630233" cy="1259205"/>
@@ -11438,11 +11480,11 @@
         <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11744,6 +11786,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor theme="4" tint="0.3999755851924192"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L35"/>
@@ -12095,7 +12138,7 @@
         <v>30</v>
       </c>
       <c r="H18" s="173" t="n"/>
-      <c r="I18" s="131">
+      <c r="I18" s="187">
         <f>IF(H18="","",G18*H18/5)</f>
         <v/>
       </c>
@@ -12120,7 +12163,7 @@
         <v>25</v>
       </c>
       <c r="H19" s="173" t="n"/>
-      <c r="I19" s="131">
+      <c r="I19" s="187">
         <f>IF(H19="","",G19*H19/5)</f>
         <v/>
       </c>
@@ -12145,7 +12188,7 @@
         <v>15</v>
       </c>
       <c r="H20" s="173" t="n"/>
-      <c r="I20" s="131">
+      <c r="I20" s="187">
         <f>IF(H20="","",G20*H20/5)</f>
         <v/>
       </c>
@@ -12170,7 +12213,7 @@
         <v>10</v>
       </c>
       <c r="H21" s="173" t="n"/>
-      <c r="I21" s="131">
+      <c r="I21" s="187">
         <f>IF(H21="","",G21*H21/5)</f>
         <v/>
       </c>
@@ -12195,7 +12238,7 @@
         <v>10</v>
       </c>
       <c r="H22" s="173" t="n"/>
-      <c r="I22" s="131">
+      <c r="I22" s="187">
         <f>IF(H22="","",G22*H22/5)</f>
         <v/>
       </c>
@@ -12220,7 +12263,7 @@
         <v>10</v>
       </c>
       <c r="H23" s="173" t="n"/>
-      <c r="I23" s="131">
+      <c r="I23" s="187">
         <f>IF(H23="","",G23*H23/5)</f>
         <v/>
       </c>
@@ -12244,7 +12287,7 @@
         <v/>
       </c>
       <c r="H24" s="43" t="n"/>
-      <c r="I24" s="134">
+      <c r="I24" s="188">
         <f>IF(COUNT(H18:H23)&lt;ROWS(H18:H23),"",SUM(I18:I23))</f>
         <v/>
       </c>
@@ -12566,6 +12609,17 @@
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="A13:B13"/>
   </mergeCells>
+  <conditionalFormatting sqref="J24:L24">
+    <cfRule type="expression" priority="1" dxfId="856" stopIfTrue="1">
+      <formula>ISNUMBER(SEARCH("NO APROBADO",$J$24))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="857" stopIfTrue="1">
+      <formula>ISNUMBER(SEARCH("CONDICIONADO",$J$24))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="858" stopIfTrue="1">
+      <formula>ISNUMBER(SEARCH("APROBADO",$J$24))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.7" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>

--- a/public/plantilla-cal-proveedores.xlsx
+++ b/public/plantilla-cal-proveedores.xlsx
@@ -11444,47 +11444,47 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>2</col>
-      <colOff>862393</colOff>
-      <row>5</row>
-      <rowOff>131445</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>862393</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>131445</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="2630233" cy="1259205"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <xdr:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
